--- a/Control_Asistencia_Montana.xlsx
+++ b/Control_Asistencia_Montana.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Empleados" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Horario_Semanal" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Registro" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Historial_Nomina" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="88">
   <si>
     <t xml:space="preserve">Codigo</t>
   </si>
@@ -45,6 +46,33 @@
     <t xml:space="preserve">Fecha_Ingreso</t>
   </si>
   <si>
+    <t xml:space="preserve">Cedula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direccion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telefono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuenta_Bancaria</t>
+  </si>
+  <si>
     <t xml:space="preserve">E01</t>
   </si>
   <si>
@@ -202,6 +230,63 @@
   </si>
   <si>
     <t xml:space="preserve">Foto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha_Cierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Periodo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Periodo_Inicio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Periodo_Fin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sueldo_Basico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auxilio_Transporte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recargo_Nocturno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recargo_DomFest_Diurno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recargo_DomFest_Nocturno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HED_DomFest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEN_DomFest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total_Devengado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total_Deducido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neto_Pagado</t>
   </si>
 </sst>
 </file>
@@ -648,7 +733,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -656,7 +741,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="8" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -680,6 +766,33 @@
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -690,13 +803,22 @@
       <c r="E2" s="3"/>
       <c r="F2" s="4"/>
       <c r="G2" s="5"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>1111</v>
@@ -706,17 +828,26 @@
         <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="5"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>2222</v>
@@ -726,17 +857,26 @@
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="5"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>3333</v>
@@ -746,17 +886,26 @@
         <v>1</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="5"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>4444</v>
@@ -766,17 +915,26 @@
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="5"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>5555</v>
@@ -786,17 +944,26 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="5"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>6666</v>
@@ -806,17 +973,26 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>7777</v>
@@ -826,17 +1002,26 @@
         <v>1</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="5"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>8888</v>
@@ -846,17 +1031,26 @@
         <v>1</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="5"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>9191</v>
@@ -866,17 +1060,26 @@
         <v>1</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="5"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>9292</v>
@@ -886,17 +1089,26 @@
         <v>1</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="5"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>9393</v>
@@ -906,17 +1118,26 @@
         <v>1</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="5"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>9494</v>
@@ -926,10 +1147,19 @@
         <v>1</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="5"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -959,28 +1189,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -993,322 +1223,322 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="J2" s="7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1342,37 +1572,124 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>59</v>
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="1" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Control_Asistencia_Montana.xlsx
+++ b/Control_Asistencia_Montana.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Horario_Semanal" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Registro" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Historial_Nomina" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Novedades" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="96">
   <si>
     <t xml:space="preserve">Codigo</t>
   </si>
@@ -73,6 +74,15 @@
     <t xml:space="preserve">Cuenta_Bancaria</t>
   </si>
   <si>
+    <t xml:space="preserve">Cargo_Confianza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo_Personal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLANTA</t>
+  </si>
+  <si>
     <t xml:space="preserve">E01</t>
   </si>
   <si>
@@ -142,6 +152,9 @@
     <t xml:space="preserve">Salón fin de semana</t>
   </si>
   <si>
+    <t xml:space="preserve">TURNO</t>
+  </si>
+  <si>
     <t xml:space="preserve">E10</t>
   </si>
   <si>
@@ -287,6 +300,18 @@
   </si>
   <si>
     <t xml:space="preserve">Neto_Pagado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creado_En</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estado</t>
   </si>
 </sst>
 </file>
@@ -733,7 +758,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -742,7 +767,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="8" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="8" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -793,6 +819,12 @@
       </c>
       <c r="P1" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -812,13 +844,20 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
+      <c r="Q2" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>1111</v>
@@ -828,7 +867,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="5"/>
@@ -841,13 +880,20 @@
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
+      <c r="Q3" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>2222</v>
@@ -857,7 +903,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="5"/>
@@ -870,13 +916,20 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
+      <c r="Q4" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>3333</v>
@@ -886,7 +939,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="5"/>
@@ -899,13 +952,20 @@
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
+      <c r="Q5" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>4444</v>
@@ -915,7 +975,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="5"/>
@@ -928,13 +988,20 @@
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
+      <c r="Q6" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>5555</v>
@@ -944,7 +1011,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="5"/>
@@ -957,13 +1024,20 @@
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
+      <c r="Q7" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>6666</v>
@@ -973,7 +1047,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
@@ -986,13 +1060,20 @@
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
+      <c r="Q8" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>7777</v>
@@ -1002,7 +1083,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="5"/>
@@ -1015,13 +1096,20 @@
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
+      <c r="Q9" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>8888</v>
@@ -1031,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="5"/>
@@ -1044,13 +1132,20 @@
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
+      <c r="Q10" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>9191</v>
@@ -1060,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="5"/>
@@ -1073,13 +1168,20 @@
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
+      <c r="Q11" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>9292</v>
@@ -1089,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="5"/>
@@ -1102,13 +1204,20 @@
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
+      <c r="Q12" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>9393</v>
@@ -1118,7 +1227,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="5"/>
@@ -1131,13 +1240,20 @@
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
+      <c r="Q13" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>9494</v>
@@ -1147,7 +1263,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="5"/>
@@ -1160,6 +1276,13 @@
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
+      <c r="Q14" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1189,28 +1312,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1223,322 +1346,322 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="J2" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1572,37 +1695,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1624,72 +1747,115 @@
   <dimension ref="A1:U1"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="1" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
